--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N103_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N103_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.37010917358833</v>
+        <v>2.985142740708103</v>
       </c>
       <c r="D2" t="n">
-        <v>69.33513251566923</v>
+        <v>11.26695903379625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8456707187637252</v>
+        <v>0.1374214917991054</v>
       </c>
       <c r="F2" t="n">
-        <v>12.76612454623181</v>
+        <v>2.074495238762669</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.48871622298621</v>
+        <v>3.329416386235259</v>
       </c>
       <c r="D3" t="n">
-        <v>63.12803201151991</v>
+        <v>10.25830520187199</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8456707187637252</v>
+        <v>0.1374214917991054</v>
       </c>
       <c r="F3" t="n">
-        <v>12.76612454623181</v>
+        <v>2.074495238762669</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.60107523773828</v>
+        <v>3.02267472613247</v>
       </c>
       <c r="D4" t="n">
-        <v>36.44432432506061</v>
+        <v>5.922202702822348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8456707187637252</v>
+        <v>0.1374214917991054</v>
       </c>
       <c r="F4" t="n">
-        <v>12.76612454623181</v>
+        <v>2.074495238762669</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.61367587116547</v>
+        <v>3.187222329064388</v>
       </c>
       <c r="D5" t="n">
-        <v>48.89878504767088</v>
+        <v>7.946052570246519</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8456707187637252</v>
+        <v>0.1374214917991054</v>
       </c>
       <c r="F5" t="n">
-        <v>12.76612454623181</v>
+        <v>2.074495238762669</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
